--- a/Data/EXCEL/Transfer/salemon/202206/6793-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6793-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB730D8-5CD4-4050-A5D8-DDB0454310C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A31AE79A-6427-48F1-B61F-9783B85D1B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6793-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,52 +1385,52 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>77.3</v>
+        <v>60.1</v>
       </c>
       <c r="C5" s="7">
-        <v>60.1</v>
+        <v>51</v>
       </c>
       <c r="D5" s="7">
-        <v>77.900000000000006</v>
+        <v>61.8</v>
       </c>
       <c r="E5" s="7">
-        <v>60</v>
+        <v>50.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-17.2</v>
+        <v>-9.1</v>
       </c>
       <c r="G5" s="8">
-        <v>-22.25</v>
+        <v>-15.14</v>
       </c>
       <c r="H5" s="9">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="I5" s="8">
-        <v>-0.84</v>
+        <v>0.252</v>
+      </c>
+      <c r="I5" s="10">
+        <v>3.53</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K5" s="9">
-        <v>0.749</v>
+        <v>1</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M5" s="9">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="N5" s="8">
-        <v>-0.84</v>
+        <v>0.252</v>
+      </c>
+      <c r="N5" s="10">
+        <v>3.53</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="9">
-        <v>0.749</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="9" t="s">
         <v>17</v>
@@ -1438,52 +1438,52 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>84.6</v>
+        <v>77.3</v>
       </c>
       <c r="C6" s="7">
-        <v>77.3</v>
+        <v>60.1</v>
       </c>
       <c r="D6" s="7">
-        <v>91.5</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="E6" s="7">
-        <v>74.2</v>
+        <v>60</v>
       </c>
       <c r="F6" s="8">
-        <v>-7.3</v>
+        <v>-17.2</v>
       </c>
       <c r="G6" s="8">
-        <v>-8.6300000000000008</v>
+        <v>-22.25</v>
       </c>
       <c r="H6" s="9">
-        <v>0.246</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="I6" s="8">
-        <v>-5.39</v>
+        <v>-0.84</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="9">
-        <v>0.505</v>
+        <v>0.749</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="9">
-        <v>0.246</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="N6" s="8">
-        <v>-5.39</v>
+        <v>-0.84</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P6" s="9">
-        <v>0.505</v>
+        <v>0.749</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>17</v>
@@ -1491,52 +1491,52 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>90.9</v>
+        <v>84.6</v>
       </c>
       <c r="C7" s="7">
-        <v>84.6</v>
+        <v>77.3</v>
       </c>
       <c r="D7" s="7">
-        <v>93</v>
+        <v>91.5</v>
       </c>
       <c r="E7" s="7">
-        <v>79.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="F7" s="8">
-        <v>-6.3</v>
+        <v>-7.3</v>
       </c>
       <c r="G7" s="8">
-        <v>-6.93</v>
+        <v>-8.6300000000000008</v>
       </c>
       <c r="H7" s="9">
-        <v>0.26</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>17</v>
+        <v>0.246</v>
+      </c>
+      <c r="I7" s="8">
+        <v>-5.39</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="9">
-        <v>0.26</v>
+        <v>0.505</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M7" s="9">
-        <v>0.26</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>17</v>
+        <v>0.246</v>
+      </c>
+      <c r="N7" s="8">
+        <v>-5.39</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="9">
-        <v>0.26</v>
+        <v>0.505</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>17</v>
@@ -1544,28 +1544,28 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>89.7</v>
+        <v>90.9</v>
       </c>
       <c r="C8" s="7">
-        <v>90.9</v>
+        <v>84.6</v>
       </c>
       <c r="D8" s="7">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E8" s="7">
-        <v>89.4</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1.34</v>
+        <v>79.599999999999994</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-6.3</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-6.93</v>
       </c>
       <c r="H8" s="9">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>17</v>
@@ -1574,13 +1574,13 @@
         <v>17</v>
       </c>
       <c r="K8" s="9">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M8" s="9">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>17</v>
@@ -1589,7 +1589,7 @@
         <v>17</v>
       </c>
       <c r="P8" s="9">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>17</v>
@@ -1597,25 +1597,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>92.2</v>
+        <v>89.7</v>
       </c>
       <c r="C9" s="7">
-        <v>89.7</v>
+        <v>90.9</v>
       </c>
       <c r="D9" s="7">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" s="7">
-        <v>85.6</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-2.71</v>
+        <v>89.4</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1.34</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1650,25 +1650,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>91.3</v>
+        <v>92.2</v>
       </c>
       <c r="C10" s="7">
-        <v>92.2</v>
+        <v>89.7</v>
       </c>
       <c r="D10" s="7">
-        <v>95.3</v>
+        <v>103</v>
       </c>
       <c r="E10" s="7">
-        <v>77.3</v>
-      </c>
-      <c r="F10" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.99</v>
+        <v>85.6</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-2.71</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1703,25 +1703,25 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>97.9</v>
+        <v>91.3</v>
       </c>
       <c r="C11" s="7">
-        <v>91.3</v>
+        <v>92.2</v>
       </c>
       <c r="D11" s="7">
-        <v>109.5</v>
+        <v>95.3</v>
       </c>
       <c r="E11" s="7">
-        <v>89.6</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-6.6</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-6.74</v>
+        <v>77.3</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.99</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1756,25 +1756,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>99.8</v>
+        <v>97.9</v>
       </c>
       <c r="C12" s="7">
-        <v>97.9</v>
+        <v>91.3</v>
       </c>
       <c r="D12" s="7">
-        <v>103</v>
+        <v>109.5</v>
       </c>
       <c r="E12" s="7">
-        <v>91</v>
+        <v>89.6</v>
       </c>
       <c r="F12" s="8">
-        <v>-1.9</v>
+        <v>-6.6</v>
       </c>
       <c r="G12" s="8">
-        <v>-1.9</v>
+        <v>-6.74</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1809,25 +1809,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>93.1</v>
+        <v>99.8</v>
       </c>
       <c r="C13" s="7">
-        <v>99.8</v>
+        <v>97.9</v>
       </c>
       <c r="D13" s="7">
-        <v>115.5</v>
+        <v>103</v>
       </c>
       <c r="E13" s="7">
-        <v>87.3</v>
-      </c>
-      <c r="F13" s="10">
-        <v>6.7</v>
-      </c>
-      <c r="G13" s="10">
-        <v>7.2</v>
+        <v>91</v>
+      </c>
+      <c r="F13" s="8">
+        <v>-1.9</v>
+      </c>
+      <c r="G13" s="8">
+        <v>-1.9</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1862,25 +1862,25 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>119</v>
+        <v>93.1</v>
       </c>
       <c r="C14" s="7">
-        <v>93.1</v>
+        <v>99.8</v>
       </c>
       <c r="D14" s="7">
-        <v>123</v>
+        <v>115.5</v>
       </c>
       <c r="E14" s="7">
-        <v>85.6</v>
-      </c>
-      <c r="F14" s="8">
-        <v>-25.9</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-21.76</v>
+        <v>87.3</v>
+      </c>
+      <c r="F14" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="G14" s="10">
+        <v>7.2</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1915,25 +1915,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>126.5</v>
+        <v>119</v>
       </c>
       <c r="C15" s="7">
-        <v>119</v>
+        <v>93.1</v>
       </c>
       <c r="D15" s="7">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E15" s="7">
-        <v>115</v>
+        <v>85.6</v>
       </c>
       <c r="F15" s="8">
-        <v>-7.5</v>
+        <v>-25.9</v>
       </c>
       <c r="G15" s="8">
-        <v>-5.93</v>
+        <v>-21.76</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1968,25 +1968,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
         <v>126.5</v>
       </c>
       <c r="C16" s="7">
-        <v>126.5</v>
+        <v>119</v>
       </c>
       <c r="D16" s="7">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E16" s="7">
-        <v>123.5</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="F16" s="8">
+        <v>-7.5</v>
+      </c>
+      <c r="G16" s="8">
+        <v>-5.93</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2021,25 +2021,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>143.5</v>
+        <v>126.5</v>
       </c>
       <c r="C17" s="7">
         <v>126.5</v>
       </c>
       <c r="D17" s="7">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E17" s="7">
-        <v>113.5</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-17</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-11.85</v>
+        <v>123.5</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2074,25 +2074,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>120</v>
+        <v>143.5</v>
       </c>
       <c r="C18" s="7">
-        <v>143.5</v>
+        <v>126.5</v>
       </c>
       <c r="D18" s="7">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E18" s="7">
-        <v>115.5</v>
-      </c>
-      <c r="F18" s="10">
-        <v>23.5</v>
-      </c>
-      <c r="G18" s="10">
-        <v>19.579999999999998</v>
+        <v>113.5</v>
+      </c>
+      <c r="F18" s="8">
+        <v>-17</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-11.85</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2127,25 +2127,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>91.2</v>
+        <v>120</v>
       </c>
       <c r="C19" s="7">
-        <v>120</v>
+        <v>143.5</v>
       </c>
       <c r="D19" s="7">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="E19" s="7">
-        <v>91</v>
+        <v>115.5</v>
       </c>
       <c r="F19" s="10">
-        <v>28.8</v>
+        <v>23.5</v>
       </c>
       <c r="G19" s="10">
-        <v>31.58</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2180,25 +2180,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>82.7</v>
+        <v>91.2</v>
       </c>
       <c r="C20" s="7">
-        <v>91.2</v>
+        <v>120</v>
       </c>
       <c r="D20" s="7">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="E20" s="7">
-        <v>80.5</v>
+        <v>91</v>
       </c>
       <c r="F20" s="10">
-        <v>8.5</v>
+        <v>28.8</v>
       </c>
       <c r="G20" s="10">
-        <v>10.28</v>
+        <v>31.58</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2233,25 +2233,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>91.3</v>
+        <v>82.7</v>
       </c>
       <c r="C21" s="7">
-        <v>82.7</v>
+        <v>91.2</v>
       </c>
       <c r="D21" s="7">
-        <v>91.5</v>
+        <v>96</v>
       </c>
       <c r="E21" s="7">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-8.6</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-9.42</v>
+        <v>80.5</v>
+      </c>
+      <c r="F21" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="G21" s="10">
+        <v>10.28</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2286,25 +2286,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>94.8</v>
+        <v>91.3</v>
       </c>
       <c r="C22" s="7">
-        <v>91.3</v>
+        <v>82.7</v>
       </c>
       <c r="D22" s="7">
-        <v>98.4</v>
+        <v>91.5</v>
       </c>
       <c r="E22" s="7">
-        <v>83</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="F22" s="8">
-        <v>-3.5</v>
+        <v>-8.6</v>
       </c>
       <c r="G22" s="8">
-        <v>-3.69</v>
+        <v>-9.42</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2312,14 +2312,14 @@
       <c r="I22" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="8">
-        <v>-100</v>
+      <c r="J22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="9">
         <v>0</v>
       </c>
-      <c r="L22" s="8">
-        <v>-100</v>
+      <c r="L22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="9">
         <v>0</v>
@@ -2327,37 +2327,37 @@
       <c r="N22" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O22" s="8">
-        <v>-100</v>
+      <c r="O22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P22" s="9">
         <v>0</v>
       </c>
-      <c r="Q22" s="8">
-        <v>-100</v>
+      <c r="Q22" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>95.3</v>
+        <v>94.8</v>
       </c>
       <c r="C23" s="7">
-        <v>94.8</v>
+        <v>91.3</v>
       </c>
       <c r="D23" s="7">
-        <v>100.5</v>
+        <v>98.4</v>
       </c>
       <c r="E23" s="7">
-        <v>73.5</v>
+        <v>83</v>
       </c>
       <c r="F23" s="8">
-        <v>-0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="G23" s="8">
-        <v>-0.52</v>
+        <v>-3.69</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2392,25 +2392,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
         <v>95.3</v>
       </c>
       <c r="C24" s="7">
-        <v>95.3</v>
+        <v>94.8</v>
       </c>
       <c r="D24" s="7">
-        <v>106.5</v>
+        <v>100.5</v>
       </c>
       <c r="E24" s="7">
-        <v>61</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
+        <v>73.5</v>
+      </c>
+      <c r="F24" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="G24" s="8">
+        <v>-0.52</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2418,14 +2418,14 @@
       <c r="I24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>17</v>
+      <c r="J24" s="8">
+        <v>-100</v>
       </c>
       <c r="K24" s="9">
         <v>0</v>
       </c>
-      <c r="L24" s="9" t="s">
-        <v>17</v>
+      <c r="L24" s="8">
+        <v>-100</v>
       </c>
       <c r="M24" s="9">
         <v>0</v>
@@ -2433,37 +2433,37 @@
       <c r="N24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O24" s="9" t="s">
-        <v>17</v>
+      <c r="O24" s="8">
+        <v>-100</v>
       </c>
       <c r="P24" s="9">
         <v>0</v>
       </c>
-      <c r="Q24" s="9" t="s">
-        <v>17</v>
+      <c r="Q24" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>17</v>
+        <v>44105</v>
+      </c>
+      <c r="B25" s="7">
+        <v>95.3</v>
+      </c>
+      <c r="C25" s="7">
+        <v>95.3</v>
+      </c>
+      <c r="D25" s="7">
+        <v>106.5</v>
+      </c>
+      <c r="E25" s="7">
+        <v>61</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2498,54 +2498,107 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
+        <v>44075</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
         <v>44044</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P26" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="9" t="s">
+      <c r="B27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="9" t="s">
         <v>17</v>
       </c>
     </row>
